--- a/inferences/jesuita-entrada_totals.xlsx
+++ b/inferences/jesuita-entrada_totals.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet_name_1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet_name_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15440000</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15460000</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15480000</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17360000</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16280000</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16780000</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16270000</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>15820000</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16410000</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16410000</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>000000</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>000000</t>
+          <t>00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>16100000</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>16100000</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>15530000</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15530000</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">

--- a/inferences/jesuita-entrada_totals.xlsx
+++ b/inferences/jesuita-entrada_totals.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
